--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:56:12+00:00</t>
+    <t>2026-03-06T09:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -288,17 +288,17 @@
     <t>SavoirFaire.dateAbandon</t>
   </si>
   <si>
-    <t>Specialite.exerciceProfessionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel)
+    <t>Specialite.ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel
 </t>
   </si>
   <si>
-    <t>Lien vers la classe ExerciceProfessionnel.</t>
-  </si>
-  <si>
-    <t>SavoirFaire.exerciceProfessionnel</t>
+    <t>Lien vers la classe ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t>SavoirFaire.ExerciceProfessionnel</t>
   </si>
   <si>
     <t>Specialite.specialite</t>
@@ -612,8 +612,8 @@
   <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="26.2265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.2265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.25390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -622,7 +622,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -643,7 +643,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="27.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="27.42578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T09:16:42+00:00</t>
+    <t>2026-04-20T07:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:14:21+00:00</t>
+    <t>2026-04-20T13:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:39:43+00:00</t>
+    <t>2026-04-20T13:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:49:18+00:00</t>
+    <t>2026-04-20T13:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:52:11+00:00</t>
+    <t>2026-04-20T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:01:02+00:00</t>
+    <t>2026-04-20T14:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:11:31+00:00</t>
+    <t>2026-04-20T14:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-Specialite.xlsx
+++ b/main/ig/StructureDefinition-Specialite.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:36:06+00:00</t>
+    <t>2026-04-20T14:56:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
